--- a/artfynd/A 35214-2026 artfynd.xlsx
+++ b/artfynd/A 35214-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136194227</v>
       </c>
       <c r="B2" t="n">
-        <v>93394</v>
+        <v>93397</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -915,7 +915,7 @@
         <v>136194230</v>
       </c>
       <c r="B4" t="n">
-        <v>92123</v>
+        <v>92126</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 35214-2026 artfynd.xlsx
+++ b/artfynd/A 35214-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136194227</v>
       </c>
       <c r="B2" t="n">
-        <v>93397</v>
+        <v>93398</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -915,7 +915,7 @@
         <v>136194230</v>
       </c>
       <c r="B4" t="n">
-        <v>92126</v>
+        <v>92127</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 35214-2026 artfynd.xlsx
+++ b/artfynd/A 35214-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136194227</v>
       </c>
       <c r="B2" t="n">
-        <v>93398</v>
+        <v>93403</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -915,7 +915,7 @@
         <v>136194230</v>
       </c>
       <c r="B4" t="n">
-        <v>92127</v>
+        <v>92132</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1026,7 +1026,7 @@
         <v>136194229</v>
       </c>
       <c r="B5" t="n">
-        <v>80594</v>
+        <v>80596</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1137,7 +1137,7 @@
         <v>136194228</v>
       </c>
       <c r="B6" t="n">
-        <v>79232</v>
+        <v>79234</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 35214-2026 artfynd.xlsx
+++ b/artfynd/A 35214-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136194227</v>
       </c>
       <c r="B2" t="n">
-        <v>93403</v>
+        <v>93405</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -915,7 +915,7 @@
         <v>136194230</v>
       </c>
       <c r="B4" t="n">
-        <v>92132</v>
+        <v>92134</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
